--- a/Task2/tco-model.xlsx
+++ b/Task2/tco-model.xlsx
@@ -4172,7 +4172,7 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>7200</v>
+        <v>2900</v>
       </c>
       <c r="E7" s="22">
         <f>IF($D7="","",$D7*INDEX(Допущения!$C$25:$G$30,MATCH($C7,Допущения!$B$25:$B$30,0),1))</f>
@@ -4201,7 +4201,7 @@
       <c r="K7" s="23" t="n"/>
       <c r="L7" s="24" t="inlineStr">
         <is>
-          <t>Managed-контейнеры (Cloud Run, ECS Fargate или аналог): 2-4 инстанса Go-монолита + воркеры</t>
+          <t>AWS af-south-1: Fargate ARM 4 задачи × (1 vCPU, 2 ГБ) $156 + ALB $36 + NAT $53 = $245/мес</t>
         </is>
       </c>
     </row>
@@ -4217,7 +4217,7 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>6000</v>
+        <v>3200</v>
       </c>
       <c r="E8" s="22">
         <f>IF($D8="","",$D8*INDEX(Допущения!$C$25:$G$30,MATCH($C8,Допущения!$B$25:$B$30,0),1))</f>
@@ -4246,7 +4246,7 @@
       <c r="K8" s="23" t="n"/>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t>Managed PostgreSQL HA: primary + standby</t>
+          <t>RDS PostgreSQL db.t4g.large Multi-AZ $239 + 100 ГБ gp3 $30 = $270/мес</t>
         </is>
       </c>
     </row>
@@ -4262,7 +4262,7 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="E9" s="22">
         <f>IF($D9="","",$D9*INDEX(Допущения!$C$25:$G$30,MATCH($C9,Допущения!$B$25:$B$30,0),1))</f>
@@ -4291,7 +4291,7 @@
       <c r="K9" s="23" t="n"/>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>Объектное хранилище: фото 5000 SKU, бэкапы</t>
+          <t>S3 300 ГБ × $0,0274 + запросы = $15/мес: фото 5000 SKU, бэкапы</t>
         </is>
       </c>
     </row>
@@ -4307,7 +4307,7 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>4800</v>
+        <v>3200</v>
       </c>
       <c r="E10" s="22">
         <f>IF($D10="","",$D10*INDEX(Допущения!$C$25:$G$30,MATCH($C10,Допущения!$B$25:$B$30,0),1))</f>
@@ -4336,7 +4336,7 @@
       <c r="K10" s="23" t="n"/>
       <c r="L10" s="24" t="inlineStr">
         <is>
-          <t>CDN для фото и статики, WebP, кеш на краю для 3G</t>
+          <t>CloudFront Южная Африка: 3 ТБ/мес, 1 ТБ бесплатно, $0,11/ГБ + запросы = $265/мес</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4352,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>600</v>
+        <v>200</v>
       </c>
       <c r="E11" s="22">
         <f>IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),1))</f>
@@ -4381,7 +4381,7 @@
       <c r="K11" s="23" t="n"/>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>Managed-очередь (SQS, Pub/Sub) для уведомлений и вебхуков</t>
+          <t>SQS для уведомлений и вебхуков, ~30 млн запросов/мес. Оценка</t>
         </is>
       </c>
     </row>
@@ -4397,7 +4397,7 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>3600</v>
+        <v>1000</v>
       </c>
       <c r="E12" s="22">
         <f>IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),1))</f>
@@ -4426,7 +4426,7 @@
       <c r="K12" s="23" t="n"/>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>Warm standby: реплика БД и бэкапы во втором регионе</t>
+          <t>Warm standby: реплика db.t4g.medium во втором регионе + копии снапшотов = $80/мес</t>
         </is>
       </c>
     </row>
@@ -4442,7 +4442,7 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>8400</v>
+        <v>900</v>
       </c>
       <c r="E13" s="22">
         <f>IF($D13="","",$D13*INDEX(Допущения!$C$25:$G$30,MATCH($C13,Допущения!$B$25:$B$30,0),1))</f>
@@ -4471,7 +4471,7 @@
       <c r="K13" s="23" t="n"/>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t>Локальный провайдер в Нигерии: хранилище ПДн, 2 ВМ + БД</t>
+          <t>Layer3 Лагос: 2 ВМ 2 vCPU / 4 ГБ / 128 ГБ по ₦39 903 + бэкап = $75/мес. Хранилище ПДн</t>
         </is>
       </c>
     </row>
@@ -4494,13 +4494,13 @@
         <v>0</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>120000</v>
+        <v>35000</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>160000</v>
+        <v>48000</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>200000</v>
+        <v>62000</v>
       </c>
       <c r="J14" s="22">
         <f>SUM(E14:I14)</f>
@@ -4509,7 +4509,7 @@
       <c r="K14" s="23" t="n"/>
       <c r="L14" s="24" t="inlineStr">
         <is>
-          <t>Переход на мультирегион с Год 3 по триггеру нагрузки. Числа введены вручную</t>
+          <t>Копия compute и БД во втором регионе с Год 3 по триггеру нагрузки. Числа введены вручную</t>
         </is>
       </c>
     </row>
@@ -7304,7 +7304,7 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>21600</v>
+        <v>7600</v>
       </c>
       <c r="E7" s="22">
         <f>IF($D7="","",$D7*INDEX(Допущения!$C$25:$G$30,MATCH($C7,Допущения!$B$25:$B$30,0),1))</f>
@@ -7333,7 +7333,7 @@
       <c r="K7" s="23" t="n"/>
       <c r="L7" s="24" t="inlineStr">
         <is>
-          <t>Managed Kubernetes, 1 кластер, 6-8 нод</t>
+          <t>EKS $73 + 6 нод m7g.large × $79 + ALB $36 + NAT $53 = $635/мес</t>
         </is>
       </c>
     </row>
@@ -7349,7 +7349,7 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>14400</v>
+        <v>9700</v>
       </c>
       <c r="E8" s="22">
         <f>IF($D8="","",$D8*INDEX(Допущения!$C$25:$G$30,MATCH($C8,Допущения!$B$25:$B$30,0),1))</f>
@@ -7378,7 +7378,7 @@
       <c r="K8" s="23" t="n"/>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t>3 managed PostgreSQL HA, БД на группу сервисов</t>
+          <t>3 × RDS PostgreSQL db.t4g.large Multi-AZ с хранилищем = $810/мес</t>
         </is>
       </c>
     </row>
@@ -7394,7 +7394,7 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>1200</v>
+        <v>200</v>
       </c>
       <c r="E9" s="22">
         <f>IF($D9="","",$D9*INDEX(Допущения!$C$25:$G$30,MATCH($C9,Допущения!$B$25:$B$30,0),1))</f>
@@ -7423,7 +7423,7 @@
       <c r="K9" s="23" t="n"/>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>Объектное хранилище: фото, бэкапы</t>
+          <t>S3: фото, бэкапы</t>
         </is>
       </c>
     </row>
@@ -7439,7 +7439,7 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>4800</v>
+        <v>3200</v>
       </c>
       <c r="E10" s="22">
         <f>IF($D10="","",$D10*INDEX(Допущения!$C$25:$G$30,MATCH($C10,Допущения!$B$25:$B$30,0),1))</f>
@@ -7468,7 +7468,7 @@
       <c r="K10" s="23" t="n"/>
       <c r="L10" s="24" t="inlineStr">
         <is>
-          <t>CDN для фото и статики</t>
+          <t>CloudFront Южная Африка, как в V1</t>
         </is>
       </c>
     </row>
@@ -7484,7 +7484,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>7200</v>
+        <v>7500</v>
       </c>
       <c r="E11" s="22">
         <f>IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),1))</f>
@@ -7513,7 +7513,7 @@
       <c r="K11" s="23" t="n"/>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>Managed Kafka, минимальный тариф</t>
+          <t>MSK 3 брокера kafka.m7g.large × $0,27/ч + 300 ГБ = $627/мес</t>
         </is>
       </c>
     </row>
@@ -7529,7 +7529,7 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>9600</v>
+        <v>5200</v>
       </c>
       <c r="E12" s="22">
         <f>IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),1))</f>
@@ -7558,7 +7558,7 @@
       <c r="K12" s="23" t="n"/>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>Warm standby кластера во втором регионе</t>
+          <t>Warm standby: EKS + 2 ноды + 3 реплики db.t4g.medium во втором регионе = $431/мес</t>
         </is>
       </c>
     </row>
@@ -7574,7 +7574,7 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>12000</v>
+        <v>1300</v>
       </c>
       <c r="E13" s="22">
         <f>IF($D13="","",$D13*INDEX(Допущения!$C$25:$G$30,MATCH($C13,Допущения!$B$25:$B$30,0),1))</f>
@@ -7603,7 +7603,7 @@
       <c r="K13" s="23" t="n"/>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t>Нода кластера и хранилище ПДн в Нигерии</t>
+          <t>Layer3 Лагос: 2 ВМ 4 vCPU / 8 ГБ + бэкап = $107/мес. Нода и хранилище ПДн</t>
         </is>
       </c>
     </row>
@@ -7626,13 +7626,13 @@
         <v>0</v>
       </c>
       <c r="G14" s="17" t="n">
-        <v>150000</v>
+        <v>75000</v>
       </c>
       <c r="H14" s="17" t="n">
-        <v>200000</v>
+        <v>100000</v>
       </c>
       <c r="I14" s="17" t="n">
-        <v>250000</v>
+        <v>130000</v>
       </c>
       <c r="J14" s="22">
         <f>SUM(E14:I14)</f>
@@ -7641,7 +7641,7 @@
       <c r="K14" s="23" t="n"/>
       <c r="L14" s="24" t="inlineStr">
         <is>
-          <t>Переход на мультирегион с Год 3. Числа введены вручную</t>
+          <t>Копия кластера и БД во втором регионе с Год 3. Числа введены вручную</t>
         </is>
       </c>
     </row>
@@ -9274,7 +9274,7 @@
     <row r="73" ht="15" customHeight="1" s="33">
       <c r="B73" s="67" t="inlineStr">
         <is>
-          <t>V2 дороже V1 за счёт 3 дополнительных людей и кластера. Облако + SaaS в Год 1 выше лимита $5k/мес. Выигрыш в доступности Год 1-2 не окупает разницу в ФОТ на объёмах пилота.</t>
+          <t>V2 дороже V1 за счёт 3 дополнительных людей и кластера. Облако + SaaS в Год 1 укладывается в $5k/мес, но запас вдвое меньше, чем у V1. Выигрыш в доступности Год 1-2 не окупает разницу в ФОТ на объёмах пилота.</t>
         </is>
       </c>
       <c r="C73" s="68" t="n"/>
@@ -10429,7 +10429,7 @@
         </is>
       </c>
       <c r="D7" s="17" t="n">
-        <v>48000</v>
+        <v>16100</v>
       </c>
       <c r="E7" s="22">
         <f>IF($D7="","",$D7*INDEX(Допущения!$C$25:$G$30,MATCH($C7,Допущения!$B$25:$B$30,0),1))</f>
@@ -10458,7 +10458,7 @@
       <c r="K7" s="23" t="n"/>
       <c r="L7" s="24" t="inlineStr">
         <is>
-          <t>Основной кластер Kubernetes: ноды под 40-50 сервисов + Istio sidecars (А5)</t>
+          <t>EKS $73 + 15 нод m7g.large под 40-50 сервисов и Istio sidecars + ALB + NAT = $1 344/мес (А5)</t>
         </is>
       </c>
     </row>
@@ -10474,7 +10474,7 @@
         </is>
       </c>
       <c r="D8" s="17" t="n">
-        <v>18000</v>
+        <v>10700</v>
       </c>
       <c r="E8" s="22">
         <f>IF($D8="","",$D8*INDEX(Допущения!$C$25:$G$30,MATCH($C8,Допущения!$B$25:$B$30,0),1))</f>
@@ -10503,7 +10503,7 @@
       <c r="K8" s="23" t="n"/>
       <c r="L8" s="24" t="inlineStr">
         <is>
-          <t>Self-hosted Oracle и PostgreSQL на ВМ и операторах (А5)</t>
+          <t>Oracle на 2 × r6i.xlarge $491 + PostgreSQL на 3 × m7g.large $236 + EBS gp3 $168 = $895/мес (А5)</t>
         </is>
       </c>
     </row>
@@ -10519,7 +10519,7 @@
         </is>
       </c>
       <c r="D9" s="17" t="n">
-        <v>3600</v>
+        <v>700</v>
       </c>
       <c r="E9" s="22">
         <f>IF($D9="","",$D9*INDEX(Допущения!$C$25:$G$30,MATCH($C9,Допущения!$B$25:$B$30,0),1))</f>
@@ -10548,7 +10548,7 @@
       <c r="K9" s="23" t="n"/>
       <c r="L9" s="24" t="inlineStr">
         <is>
-          <t>Объектное хранилище, бэкапы трёх кластеров</t>
+          <t>S3 1 ТБ + снапшоты EBS трёх кластеров = $60/мес</t>
         </is>
       </c>
     </row>
@@ -10564,7 +10564,7 @@
         </is>
       </c>
       <c r="D10" s="17" t="n">
-        <v>4800</v>
+        <v>3200</v>
       </c>
       <c r="E10" s="22">
         <f>IF($D10="","",$D10*INDEX(Допущения!$C$25:$G$30,MATCH($C10,Допущения!$B$25:$B$30,0),1))</f>
@@ -10593,7 +10593,7 @@
       <c r="K10" s="23" t="n"/>
       <c r="L10" s="24" t="inlineStr">
         <is>
-          <t>CDN для фото и статики</t>
+          <t>CloudFront Южная Африка, как в V1</t>
         </is>
       </c>
     </row>
@@ -10609,7 +10609,7 @@
         </is>
       </c>
       <c r="D11" s="17" t="n">
-        <v>14400</v>
+        <v>7200</v>
       </c>
       <c r="E11" s="22">
         <f>IF($D11="","",$D11*INDEX(Допущения!$C$25:$G$30,MATCH($C11,Допущения!$B$25:$B$30,0),1))</f>
@@ -10638,7 +10638,7 @@
       <c r="K11" s="23" t="n"/>
       <c r="L11" s="24" t="inlineStr">
         <is>
-          <t>Self-hosted Kafka, 3 брокера × 2 региона (А5)</t>
+          <t>Self-hosted Kafka: 6 брокеров m7g.large (3 × 2 региона) + EBS 1,2 ТБ = $600/мес (А5)</t>
         </is>
       </c>
     </row>
@@ -10654,7 +10654,7 @@
         </is>
       </c>
       <c r="D12" s="17" t="n">
-        <v>48000</v>
+        <v>26900</v>
       </c>
       <c r="E12" s="22">
         <f>IF($D12="","",$D12*INDEX(Допущения!$C$25:$G$30,MATCH($C12,Допущения!$B$25:$B$30,0),1))</f>
@@ -10683,7 +10683,7 @@
       <c r="K12" s="23" t="n"/>
       <c r="L12" s="24" t="inlineStr">
         <is>
-          <t>Второй регион active-active, полная копия, RPO 0 (А5)</t>
+          <t>Второй регион active-active: копия кластера и БД = $2 239/мес, RPO 0 (А5)</t>
         </is>
       </c>
     </row>
@@ -10699,7 +10699,7 @@
         </is>
       </c>
       <c r="D13" s="17" t="n">
-        <v>30000</v>
+        <v>6600</v>
       </c>
       <c r="E13" s="22">
         <f>IF($D13="","",$D13*INDEX(Допущения!$C$25:$G$30,MATCH($C13,Допущения!$B$25:$B$30,0),1))</f>
@@ -10728,7 +10728,7 @@
       <c r="K13" s="23" t="n"/>
       <c r="L13" s="24" t="inlineStr">
         <is>
-          <t>On-prem кластер в Нигерии: колокация и аренда оборудования (А5)</t>
+          <t>Нигерия: 3 ВМ 8 vCPU / 32 ГБ у Layer3 = $554/мес. Нижняя граница: цены колокации не опубликованы (А5)</t>
         </is>
       </c>
     </row>
@@ -10841,7 +10841,7 @@
         </is>
       </c>
       <c r="D18" s="17" t="n">
-        <v>12000</v>
+        <v>4100</v>
       </c>
       <c r="E18" s="22">
         <f>IF($D18="","",$D18*INDEX(Допущения!$C$25:$G$30,MATCH($C18,Допущения!$B$25:$B$30,0),1))</f>
@@ -10870,7 +10870,7 @@
       <c r="K18" s="23" t="n"/>
       <c r="L18" s="24" t="inlineStr">
         <is>
-          <t>Self-hosted Prometheus, Loki, Jaeger, Grafana: ВМ и хранилище (А5)</t>
+          <t>Self-hosted Prometheus, Loki, Jaeger, Grafana: 3 × m7g.large + EBS 1 ТБ = $341/мес (А5)</t>
         </is>
       </c>
     </row>
@@ -12409,7 +12409,7 @@
     <row r="73" ht="15" customHeight="1" s="33">
       <c r="B73" s="67" t="inlineStr">
         <is>
-          <t>V3 самый дорогой: ФОТ 16 человек против 6, облако + SaaS в Год 1 в 3,5 раза выше лимита CFO, лицензия Oracle. Ниже ожидаемые потери от простоя, но разница не покрывает перерасход. Запуск 15.10 невозможен: только логистика по оценке CTO занимает 6 месяцев (А5).</t>
+          <t>V3 самый дорогой: ФОТ 16 человек против 6, облако + SaaS в Год 1 выше лимита CFO, лицензия Oracle. Ниже ожидаемые потери от простоя, но разница не покрывает перерасход. Запуск 15.10 невозможен: только логистика по оценке CTO занимает 6 месяцев (А5).</t>
         </is>
       </c>
       <c r="C73" s="68" t="n"/>

--- a/Task2/tco-model.xlsx
+++ b/Task2/tco-model.xlsx
@@ -1924,7 +1924,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:F38"/>
+  <dimension ref="B2:F39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="62" customWidth="1" style="33" min="2" max="2"/>
@@ -2421,44 +2421,54 @@
         </is>
       </c>
       <c r="C33" s="53" t="n">
-        <v>120000</v>
+        <v>20000</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="inlineStr">
         <is>
+          <t>2 SRE на год раньше плана, $</t>
+        </is>
+      </c>
+      <c r="C34" s="53" t="n">
+        <v>110000</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" t="inlineStr">
+        <is>
           <t>Итого цена ошибки «строим малое», $</t>
         </is>
       </c>
-      <c r="C34" s="53">
-        <f>C32+C33</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="58" t="inlineStr">
+      <c r="C35" s="53">
+        <f>SUM(C32:C34)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="58" t="inlineStr">
         <is>
           <t>Точка безубыточности по цене минуты простоя</t>
         </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>При какой цене минуты дорогой вариант окупает себя меньшим простоем, $/мин</t>
-        </is>
-      </c>
-      <c r="D37" s="53">
-        <f>(('TCO-V2'!J15+'TCO-V2'!J24+'TCO-V2'!J40+'TCO-V2'!J48)-('TCO-V1'!J15+'TCO-V1'!J24+'TCO-V1'!J40+'TCO-V1'!J48))*(1+Допущения!$C$17)/(C18-D18)</f>
-        <v/>
-      </c>
-      <c r="E37" s="53">
-        <f>(('TCO-V3'!J15+'TCO-V3'!J24+'TCO-V3'!J40+'TCO-V3'!J48)-('TCO-V1'!J15+'TCO-V1'!J24+'TCO-V1'!J40+'TCO-V1'!J48))*(1+Допущения!$C$17)/(C18-E18)</f>
-        <v/>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="inlineStr">
+        <is>
+          <t>При какой цене минуты дорогой вариант окупает себя меньшим простоем, $/мин</t>
+        </is>
+      </c>
+      <c r="D38" s="53">
+        <f>(('TCO-V2'!J15+'TCO-V2'!J24+'TCO-V2'!J40+'TCO-V2'!J48)-('TCO-V1'!J15+'TCO-V1'!J24+'TCO-V1'!J40+'TCO-V1'!J48))*(1+Допущения!$C$17)/(C18-D18)</f>
+        <v/>
+      </c>
+      <c r="E38" s="53">
+        <f>(('TCO-V3'!J15+'TCO-V3'!J24+'TCO-V3'!J40+'TCO-V3'!J48)-('TCO-V1'!J15+'TCO-V1'!J24+'TCO-V1'!J40+'TCO-V1'!J48))*(1+Допущения!$C$17)/(C18-E18)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="B39" t="inlineStr">
         <is>
           <t>Каждый вариант против V1. Инвестор: $12 000 (А1). Средний GMV в минуту: Год 1 $46, Год 5 $1 600</t>
         </is>

--- a/Task2/tco-model.xlsx
+++ b/Task2/tco-model.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\promn\PycharmProjects\my\study\solution_architecture_module_9\Task2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6BF5459-12B3-48B6-8E0A-05AF170917EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DEA29250-F60D-4195-83C7-18850F7F90EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="24196" windowHeight="14476" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
